--- a/base_datos_a.xlsx
+++ b/base_datos_a.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCB7D372-CDD8-4540-ABF8-9C2B1905C5B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C658584D-FDAD-4F06-A05C-421BF67BC87B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13740" xr2:uid="{878F31C5-4CEA-4304-87C5-39FC92D222CB}"/>
   </bookViews>
@@ -583,7 +583,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -592,7 +592,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -930,6 +929,7 @@
   <dimension ref="A1:H166"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
+    <col min="1" max="1" width="11" style="1"/>
     <col min="2" max="2" width="45.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2209,7 +2209,7 @@
       </c>
     </row>
     <row r="160" spans="1:2">
-      <c r="A160" s="4">
+      <c r="A160" s="3">
         <v>444615</v>
       </c>
       <c r="B160" t="s">
@@ -2217,7 +2217,7 @@
       </c>
     </row>
     <row r="161" spans="1:2">
-      <c r="A161" s="4">
+      <c r="A161" s="3">
         <v>44164626</v>
       </c>
       <c r="B161" t="s">
@@ -2225,7 +2225,7 @@
       </c>
     </row>
     <row r="162" spans="1:2">
-      <c r="A162" s="4">
+      <c r="A162" s="3">
         <v>43928099</v>
       </c>
       <c r="B162" t="s">
@@ -2233,7 +2233,7 @@
       </c>
     </row>
     <row r="163" spans="1:2">
-      <c r="A163" s="4">
+      <c r="A163" s="3">
         <v>10576320</v>
       </c>
       <c r="B163" t="s">
@@ -2241,7 +2241,7 @@
       </c>
     </row>
     <row r="164" spans="1:2">
-      <c r="A164" s="4">
+      <c r="A164" s="3">
         <v>73593686</v>
       </c>
       <c r="B164" t="s">
@@ -2249,7 +2249,7 @@
       </c>
     </row>
     <row r="165" spans="1:2">
-      <c r="A165" s="4">
+      <c r="A165" s="3">
         <v>41138839</v>
       </c>
       <c r="B165" t="s">
@@ -2257,7 +2257,7 @@
       </c>
     </row>
     <row r="166" spans="1:2">
-      <c r="A166" s="4">
+      <c r="A166" s="3">
         <v>41297310</v>
       </c>
       <c r="B166" t="s">
